--- a/Assets/Resources/Excel/Skill.xlsx
+++ b/Assets/Resources/Excel/Skill.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DF1ED70-1BDF-49C2-8923-656708F4C2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AD609EB-34A7-41AE-8465-74E1145DA9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>TID</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>skillIcon</t>
+  </si>
+  <si>
+    <t>skillPrefab</t>
   </si>
   <si>
     <t>skillCooltime</t>
@@ -89,7 +92,10 @@
     <t>Image_Skill_prismGrenade</t>
   </si>
   <si>
-    <t>circle</t>
+    <t>Prefab_1_PrismGrenade</t>
+  </si>
+  <si>
+    <t>circle_zone</t>
   </si>
   <si>
     <t>damage</t>
@@ -450,21 +456,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.75" customWidth="1"/>
     <col min="4" max="4" width="22.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.875" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -510,51 +518,57 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" ht="115.5">
+    <row r="2" spans="1:16" ht="115.5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2">
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2">
         <v>3</v>
       </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2">
         <v>0.5</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>1.5</v>
       </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2">
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2">
         <v>0.5</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>2.5</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Skill.xlsx
+++ b/Assets/Resources/Excel/Skill.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AD609EB-34A7-41AE-8465-74E1145DA9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21B6BD4F-F17F-4233-875B-729ADAFB9010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>TID</t>
   </si>
@@ -48,60 +48,129 @@
     <t>skillPrefab</t>
   </si>
   <si>
+    <t>mpCost</t>
+  </si>
+  <si>
     <t>skillCooltime</t>
   </si>
   <si>
-    <t>mpCost</t>
-  </si>
-  <si>
     <t>fireRange</t>
   </si>
   <si>
-    <t>areaType</t>
-  </si>
-  <si>
-    <t>areaWidth</t>
+    <t>activateTime</t>
+  </si>
+  <si>
+    <t>activateSFX</t>
+  </si>
+  <si>
+    <t>activateVFX</t>
+  </si>
+  <si>
+    <t>targetType</t>
+  </si>
+  <si>
+    <t>targetObjectCategory</t>
   </si>
   <si>
     <t>effectType_0</t>
   </si>
   <si>
+    <t>areaType_0</t>
+  </si>
+  <si>
+    <t>areaWidth_0</t>
+  </si>
+  <si>
+    <t>effectTarget_0</t>
+  </si>
+  <si>
     <t>effectDelay_0</t>
   </si>
   <si>
     <t>effectValue_0</t>
   </si>
   <si>
+    <t>effectHitSFX_0</t>
+  </si>
+  <si>
+    <t>effectHitVFX_0</t>
+  </si>
+  <si>
     <t>effectType_1</t>
   </si>
   <si>
+    <t>areaType_1</t>
+  </si>
+  <si>
+    <t>areaWidth_1</t>
+  </si>
+  <si>
+    <t>effectTarget_1</t>
+  </si>
+  <si>
     <t>effectDelay_1</t>
   </si>
   <si>
     <t>effectValue_1</t>
   </si>
   <si>
+    <t>effectHitSFX_1</t>
+  </si>
+  <si>
+    <t>effectHitVFX_1</t>
+  </si>
+  <si>
     <t>프리즘 유탄</t>
   </si>
   <si>
-    <t>소비 MP: 10
-15m 거리 이내에 프리즘 유탄을 발사합니다. 발사한 유탄은 0.5초 후에 폭발하여 반경 3m 내의 적에게 플레이어 공격력의 150%의 피해를 주고, 동일 범위 내의 시야를 2.5초 동안 확보합니다.
+    <t>소비 MP: 20
+15m 거리 내에서 지정한 지점에 프리즘 유탄을 발사합니다. 발사한 유탄은 0.5초 후에 폭발하여 반경 3m 내의 적에게 플레이어 공격력의 150%의 피해를 주고, 2.5초 동안 반경 18m 범위 내의 적을 유인하는 소음 디코이를 생성합니다.
 재사용 대기시간: 5초</t>
   </si>
   <si>
-    <t>Image_Skill_prismGrenade</t>
+    <t>Image_YuanSkill</t>
   </si>
   <si>
     <t>Prefab_1_PrismGrenade</t>
   </si>
   <si>
-    <t>circle_zone</t>
+    <t>P0.5_Skill_Activate_SFX</t>
+  </si>
+  <si>
+    <t>P0.5_Skill_Activate_VFX</t>
+  </si>
+  <si>
+    <t>cursorPoint</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
   <si>
     <t>damage</t>
   </si>
   <si>
-    <t>vision</t>
+    <t>circle</t>
+  </si>
+  <si>
+    <t>opponent</t>
+  </si>
+  <si>
+    <t>P0.5_Skill_Hit_SFX</t>
+  </si>
+  <si>
+    <t>P0.5_Skill_Hit_VFX</t>
+  </si>
+  <si>
+    <t>aggro</t>
+  </si>
+  <si>
+    <t>single</t>
+  </si>
+  <si>
+    <t>P0.5_Skill_Decoy_SFX</t>
+  </si>
+  <si>
+    <t>P0.5_Skill_Decoy_VFX</t>
   </si>
 </sst>
 </file>
@@ -456,23 +525,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.75" customWidth="1"/>
+    <col min="3" max="3" width="52.125" customWidth="1"/>
     <col min="4" max="4" width="22.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.875" customWidth="1"/>
-    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.875" customWidth="1"/>
+    <col min="12" max="12" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.625" customWidth="1"/>
+    <col min="22" max="22" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,55 +603,133 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" ht="115.5">
+    <row r="2" spans="1:29" ht="99">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2">
         <v>5</v>
-      </c>
-      <c r="G2">
-        <v>10</v>
       </c>
       <c r="H2">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2">
+      <c r="I2">
+        <v>0.2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2">
         <v>3</v>
       </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
+      <c r="Q2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2">
         <v>0.5</v>
       </c>
-      <c r="M2">
+      <c r="S2">
         <v>1.5</v>
       </c>
-      <c r="N2" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2">
+      <c r="T2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2">
+        <v>18</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2">
         <v>0.5</v>
       </c>
-      <c r="P2">
+      <c r="AA2">
         <v>2.5</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
